--- a/plm python control/wrappers/multibeam parameters/plough/plough pol rotations/plough_ramp_05_phase0.xlsx
+++ b/plm python control/wrappers/multibeam parameters/plough/plough pol rotations/plough_ramp_05_phase0.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PLM\plm python control\wrappers\multibeam parameters\plough\plough pol rotations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3D24ED-8789-4B41-B3BA-F9EF6094038C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="16200" yWindow="960" windowWidth="9060" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -52,8 +58,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,13 +96,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -134,7 +148,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -168,6 +182,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -202,9 +217,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -377,11 +393,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:D105"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -395,7 +411,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -409,7 +425,7 @@
         <v>10.55</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -423,7 +439,7 @@
         <v>138.32</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1</v>
       </c>
@@ -434,10 +450,10 @@
         <v>5</v>
       </c>
       <c r="D5">
-        <v>10.412</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
+        <v>10.412000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -448,10 +464,10 @@
         <v>6</v>
       </c>
       <c r="D6">
-        <v>86.8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>1</v>
       </c>
@@ -465,7 +481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -479,7 +495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -490,10 +506,10 @@
         <v>8</v>
       </c>
       <c r="D9">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>1</v>
       </c>
@@ -507,7 +523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>2</v>
       </c>
@@ -521,7 +537,7 @@
         <v>1.05</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -535,7 +551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -549,7 +565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>1</v>
       </c>
@@ -563,7 +579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>1</v>
       </c>
@@ -577,7 +593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -591,7 +607,7 @@
         <v>12.6</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -605,7 +621,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1</v>
       </c>
@@ -616,10 +632,10 @@
         <v>4</v>
       </c>
       <c r="D19">
-        <v>65.932</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
+        <v>66.512</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>1</v>
       </c>
@@ -630,10 +646,10 @@
         <v>5</v>
       </c>
       <c r="D20">
-        <v>10.6575</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
+        <v>10.66</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -644,10 +660,10 @@
         <v>6</v>
       </c>
       <c r="D21">
-        <v>82.59999999999999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
+        <v>79.400000000000006</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1</v>
       </c>
@@ -661,7 +677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>2</v>
       </c>
@@ -675,7 +691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -686,10 +702,10 @@
         <v>8</v>
       </c>
       <c r="D24">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1</v>
       </c>
@@ -703,7 +719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>2</v>
       </c>
@@ -717,7 +733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>0</v>
       </c>
@@ -731,7 +747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -745,7 +761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1</v>
       </c>
@@ -759,7 +775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>1</v>
       </c>
@@ -773,7 +789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>0</v>
       </c>
@@ -787,7 +803,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>0</v>
       </c>
@@ -801,7 +817,7 @@
         <v>11.25</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>1</v>
       </c>
@@ -812,10 +828,10 @@
         <v>4</v>
       </c>
       <c r="D34">
-        <v>52.532</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>52.612000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>1</v>
       </c>
@@ -829,7 +845,7 @@
         <v>11.1</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -840,10 +856,10 @@
         <v>6</v>
       </c>
       <c r="D36">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
+        <v>78.8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>1</v>
       </c>
@@ -857,7 +873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>2</v>
       </c>
@@ -871,7 +887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -882,10 +898,10 @@
         <v>8</v>
       </c>
       <c r="D39">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>1</v>
       </c>
@@ -899,7 +915,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>2</v>
       </c>
@@ -913,7 +929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -927,7 +943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>0</v>
       </c>
@@ -941,7 +957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>1</v>
       </c>
@@ -955,7 +971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1</v>
       </c>
@@ -969,7 +985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>0</v>
       </c>
@@ -983,7 +999,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>0</v>
       </c>
@@ -997,7 +1013,7 @@
         <v>12.45064130278138</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>1</v>
       </c>
@@ -1011,7 +1027,7 @@
         <v>45.692</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1</v>
       </c>
@@ -1022,10 +1038,10 @@
         <v>5</v>
       </c>
       <c r="D50">
-        <v>12.267</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
+        <v>12.266999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>0</v>
       </c>
@@ -1036,10 +1052,10 @@
         <v>6</v>
       </c>
       <c r="D51">
-        <v>76.2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
+        <v>81.8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>1</v>
       </c>
@@ -1050,10 +1066,10 @@
         <v>6</v>
       </c>
       <c r="D52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>2</v>
       </c>
@@ -1067,7 +1083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>0</v>
       </c>
@@ -1078,10 +1094,10 @@
         <v>8</v>
       </c>
       <c r="D54">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1</v>
       </c>
@@ -1095,7 +1111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>2</v>
       </c>
@@ -1109,7 +1125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>0</v>
       </c>
@@ -1123,7 +1139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>0</v>
       </c>
@@ -1137,7 +1153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1</v>
       </c>
@@ -1151,7 +1167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>1</v>
       </c>
@@ -1165,7 +1181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>0</v>
       </c>
@@ -1176,10 +1192,10 @@
         <v>4</v>
       </c>
       <c r="D62">
-        <v>11.4428341384863</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
+        <v>11.443</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>0</v>
       </c>
@@ -1190,10 +1206,10 @@
         <v>5</v>
       </c>
       <c r="D63">
-        <v>11.5901771336554</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
+        <v>11.59</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>1</v>
       </c>
@@ -1204,10 +1220,10 @@
         <v>4</v>
       </c>
       <c r="D64">
-        <v>43.392</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+        <v>43.392000000000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>1</v>
       </c>
@@ -1218,10 +1234,10 @@
         <v>5</v>
       </c>
       <c r="D65">
-        <v>11.424</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
+        <v>11.423999999999999</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -1232,10 +1248,10 @@
         <v>6</v>
       </c>
       <c r="D66">
-        <v>70.59999999999999</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
+        <v>77.599999999999994</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>1</v>
       </c>
@@ -1246,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="D67">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>2</v>
       </c>
@@ -1263,7 +1279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>0</v>
       </c>
@@ -1274,10 +1290,10 @@
         <v>8</v>
       </c>
       <c r="D69">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>1</v>
       </c>
@@ -1291,7 +1307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>2</v>
       </c>
@@ -1305,7 +1321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>0</v>
       </c>
@@ -1319,7 +1335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>0</v>
       </c>
@@ -1333,7 +1349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>1</v>
       </c>
@@ -1347,7 +1363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>1</v>
       </c>
@@ -1361,7 +1377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>0</v>
       </c>
@@ -1375,7 +1391,7 @@
         <v>10.6</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>0</v>
       </c>
@@ -1389,7 +1405,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>1</v>
       </c>
@@ -1400,10 +1416,10 @@
         <v>4</v>
       </c>
       <c r="D79">
-        <v>33.38</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
+        <v>33.380000000000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>1</v>
       </c>
@@ -1417,7 +1433,7 @@
         <v>12.79</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>0</v>
       </c>
@@ -1428,10 +1444,10 @@
         <v>6</v>
       </c>
       <c r="D81">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>1</v>
       </c>
@@ -1442,10 +1458,10 @@
         <v>6</v>
       </c>
       <c r="D82">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>2</v>
       </c>
@@ -1459,7 +1475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -1470,10 +1486,10 @@
         <v>8</v>
       </c>
       <c r="D84">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>1</v>
       </c>
@@ -1484,10 +1500,10 @@
         <v>8</v>
       </c>
       <c r="D85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>2</v>
       </c>
@@ -1501,7 +1517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>0</v>
       </c>
@@ -1515,7 +1531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>1</v>
       </c>
@@ -1543,7 +1559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>1</v>
       </c>
@@ -1557,7 +1573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>0</v>
       </c>
@@ -1571,7 +1587,7 @@
         <v>10.205</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>0</v>
       </c>
@@ -1585,7 +1601,7 @@
         <v>11.91111111111111</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>1</v>
       </c>
@@ -1599,7 +1615,7 @@
         <v>29.78</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>1</v>
       </c>
@@ -1610,10 +1626,10 @@
         <v>5</v>
       </c>
       <c r="D95">
-        <v>11.718</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
+        <v>11.731999999999999</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>0</v>
       </c>
@@ -1627,7 +1643,7 @@
         <v>66.8</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>1</v>
       </c>
@@ -1638,10 +1654,10 @@
         <v>6</v>
       </c>
       <c r="D97">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>2</v>
       </c>
@@ -1655,7 +1671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>0</v>
       </c>
@@ -1666,10 +1682,10 @@
         <v>8</v>
       </c>
       <c r="D99">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>1</v>
       </c>
@@ -1680,10 +1696,10 @@
         <v>8</v>
       </c>
       <c r="D100">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>2</v>
       </c>
@@ -1697,7 +1713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>0</v>
       </c>
@@ -1711,7 +1727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>0</v>
       </c>
@@ -1725,7 +1741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>1</v>
       </c>
@@ -1739,7 +1755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>1</v>
       </c>
